--- a/output/yearly_population_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_97_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8058</v>
+        <v>6549</v>
       </c>
       <c r="C2" t="n">
-        <v>7461</v>
+        <v>9192</v>
       </c>
       <c r="D2" t="n">
-        <v>35101</v>
+        <v>23795</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4646</v>
+        <v>3601</v>
       </c>
       <c r="C3" t="n">
-        <v>6224</v>
+        <v>6158</v>
       </c>
       <c r="D3" t="n">
-        <v>15654</v>
+        <v>14619</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3438</v>
+        <v>2814</v>
       </c>
       <c r="C4" t="n">
-        <v>4057</v>
+        <v>5388</v>
       </c>
       <c r="D4" t="n">
-        <v>9089</v>
+        <v>6921</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2070</v>
+        <v>1787</v>
       </c>
       <c r="C5" t="n">
-        <v>3680</v>
+        <v>4558</v>
       </c>
       <c r="D5" t="n">
-        <v>3452</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1139</v>
+        <v>1018</v>
       </c>
       <c r="C6" t="n">
-        <v>2609</v>
+        <v>3763</v>
       </c>
       <c r="D6" t="n">
-        <v>1295</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>533</v>
+        <v>487</v>
       </c>
       <c r="C7" t="n">
-        <v>1365</v>
+        <v>2616</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>587</v>
+        <v>1253</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>470</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7998</v>
+        <v>6856</v>
       </c>
       <c r="C2" t="n">
-        <v>11357</v>
+        <v>14037</v>
       </c>
       <c r="D2" t="n">
-        <v>30118</v>
+        <v>29108</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5003</v>
+        <v>3936</v>
       </c>
       <c r="C3" t="n">
-        <v>5971</v>
+        <v>6603</v>
       </c>
       <c r="D3" t="n">
-        <v>17246</v>
+        <v>14834</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3420</v>
+        <v>2689</v>
       </c>
       <c r="C4" t="n">
-        <v>4973</v>
+        <v>5630</v>
       </c>
       <c r="D4" t="n">
-        <v>9796</v>
+        <v>7826</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2338</v>
+        <v>1975</v>
       </c>
       <c r="C5" t="n">
-        <v>3780</v>
+        <v>4785</v>
       </c>
       <c r="D5" t="n">
-        <v>4267</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1398</v>
+        <v>1212</v>
       </c>
       <c r="C6" t="n">
-        <v>3041</v>
+        <v>4034</v>
       </c>
       <c r="D6" t="n">
-        <v>1608</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>710</v>
+        <v>631</v>
       </c>
       <c r="C7" t="n">
-        <v>1925</v>
+        <v>3109</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="C8" t="n">
-        <v>916</v>
+        <v>1801</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>784</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8942</v>
+        <v>7346</v>
       </c>
       <c r="C2" t="n">
-        <v>14986</v>
+        <v>14268</v>
       </c>
       <c r="D2" t="n">
-        <v>35705</v>
+        <v>26527</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5074</v>
+        <v>4120</v>
       </c>
       <c r="C3" t="n">
-        <v>7274</v>
+        <v>8441</v>
       </c>
       <c r="D3" t="n">
-        <v>17762</v>
+        <v>15597</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3455</v>
+        <v>2696</v>
       </c>
       <c r="C4" t="n">
-        <v>5310</v>
+        <v>5860</v>
       </c>
       <c r="D4" t="n">
-        <v>10642</v>
+        <v>8597</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2460</v>
+        <v>2006</v>
       </c>
       <c r="C5" t="n">
-        <v>4169</v>
+        <v>4980</v>
       </c>
       <c r="D5" t="n">
-        <v>4892</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1617</v>
+        <v>1370</v>
       </c>
       <c r="C6" t="n">
-        <v>3288</v>
+        <v>4294</v>
       </c>
       <c r="D6" t="n">
-        <v>1969</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>891</v>
+        <v>766</v>
       </c>
       <c r="C7" t="n">
-        <v>2383</v>
+        <v>3430</v>
       </c>
       <c r="D7" t="n">
-        <v>855</v>
+        <v>753</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>406</v>
+        <v>358</v>
       </c>
       <c r="C8" t="n">
-        <v>1302</v>
+        <v>2269</v>
       </c>
       <c r="D8" t="n">
-        <v>499</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="C9" t="n">
-        <v>601</v>
+        <v>1144</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>480</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8246</v>
+        <v>6832</v>
       </c>
       <c r="C2" t="n">
-        <v>10190</v>
+        <v>9930</v>
       </c>
       <c r="D2" t="n">
-        <v>29246</v>
+        <v>21970</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6185</v>
+        <v>4859</v>
       </c>
       <c r="C3" t="n">
-        <v>10922</v>
+        <v>12118</v>
       </c>
       <c r="D3" t="n">
-        <v>19638</v>
+        <v>16865</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2273</v>
+        <v>1853</v>
       </c>
       <c r="C4" t="n">
-        <v>6958</v>
+        <v>7874</v>
       </c>
       <c r="D4" t="n">
-        <v>10328</v>
+        <v>8113</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1494</v>
+        <v>1265</v>
       </c>
       <c r="C5" t="n">
-        <v>3222</v>
+        <v>4208</v>
       </c>
       <c r="D5" t="n">
-        <v>3244</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>823</v>
+        <v>707</v>
       </c>
       <c r="C6" t="n">
-        <v>2335</v>
+        <v>3361</v>
       </c>
       <c r="D6" t="n">
-        <v>837</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>375</v>
+        <v>330</v>
       </c>
       <c r="C7" t="n">
-        <v>1275</v>
+        <v>2223</v>
       </c>
       <c r="D7" t="n">
-        <v>489</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>588</v>
+        <v>1121</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>470</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5049</v>
+        <v>4098</v>
       </c>
       <c r="C2" t="n">
-        <v>4110</v>
+        <v>5335</v>
       </c>
       <c r="D2" t="n">
-        <v>20937</v>
+        <v>15450</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6116</v>
+        <v>4905</v>
       </c>
       <c r="C3" t="n">
-        <v>9586</v>
+        <v>10137</v>
       </c>
       <c r="D3" t="n">
-        <v>19813</v>
+        <v>16749</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3244</v>
+        <v>2566</v>
       </c>
       <c r="C4" t="n">
-        <v>8945</v>
+        <v>9927</v>
       </c>
       <c r="D4" t="n">
-        <v>11642</v>
+        <v>9282</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1671</v>
+        <v>1407</v>
       </c>
       <c r="C5" t="n">
-        <v>4851</v>
+        <v>5765</v>
       </c>
       <c r="D5" t="n">
-        <v>4091</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>991</v>
+        <v>833</v>
       </c>
       <c r="C6" t="n">
-        <v>2761</v>
+        <v>3810</v>
       </c>
       <c r="D6" t="n">
-        <v>1082</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>306</v>
       </c>
       <c r="C7" t="n">
-        <v>1677</v>
+        <v>2708</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>785</v>
+        <v>1444</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>505</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5224</v>
+        <v>4189</v>
       </c>
       <c r="C2" t="n">
-        <v>4795</v>
+        <v>9200</v>
       </c>
       <c r="D2" t="n">
-        <v>28212</v>
+        <v>16987</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4811</v>
+        <v>3851</v>
       </c>
       <c r="C3" t="n">
-        <v>6219</v>
+        <v>7097</v>
       </c>
       <c r="D3" t="n">
-        <v>18634</v>
+        <v>15446</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3822</v>
+        <v>3048</v>
       </c>
       <c r="C4" t="n">
-        <v>9072</v>
+        <v>9819</v>
       </c>
       <c r="D4" t="n">
-        <v>12621</v>
+        <v>10218</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2066</v>
+        <v>1666</v>
       </c>
       <c r="C5" t="n">
-        <v>6675</v>
+        <v>7522</v>
       </c>
       <c r="D5" t="n">
-        <v>5126</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1178</v>
+        <v>973</v>
       </c>
       <c r="C6" t="n">
-        <v>3704</v>
+        <v>4656</v>
       </c>
       <c r="D6" t="n">
-        <v>1501</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>525</v>
+        <v>445</v>
       </c>
       <c r="C7" t="n">
-        <v>2160</v>
+        <v>3160</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1150</v>
+        <v>1953</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>511</v>
+        <v>855</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
         <v>35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3119</v>
+        <v>2543</v>
       </c>
       <c r="C2" t="n">
-        <v>2248</v>
+        <v>4446</v>
       </c>
       <c r="D2" t="n">
-        <v>19679</v>
+        <v>11846</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4778</v>
+        <v>3792</v>
       </c>
       <c r="C3" t="n">
-        <v>5551</v>
+        <v>7576</v>
       </c>
       <c r="D3" t="n">
-        <v>19212</v>
+        <v>15260</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4171</v>
+        <v>3329</v>
       </c>
       <c r="C4" t="n">
-        <v>8822</v>
+        <v>9721</v>
       </c>
       <c r="D4" t="n">
-        <v>13411</v>
+        <v>10887</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2136</v>
+        <v>1722</v>
       </c>
       <c r="C5" t="n">
-        <v>8221</v>
+        <v>9136</v>
       </c>
       <c r="D5" t="n">
-        <v>5397</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>788</v>
       </c>
       <c r="C6" t="n">
-        <v>4431</v>
+        <v>5585</v>
       </c>
       <c r="D6" t="n">
-        <v>1457</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2195</v>
+        <v>3383</v>
       </c>
       <c r="D7" t="n">
-        <v>599</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>850</v>
+        <v>1412</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
         <v>34</v>
-      </c>
-      <c r="D15" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4242</v>
+        <v>3178</v>
       </c>
       <c r="C2" t="n">
-        <v>4876</v>
+        <v>6035</v>
       </c>
       <c r="D2" t="n">
-        <v>14634</v>
+        <v>13641</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3506</v>
+        <v>2816</v>
       </c>
       <c r="C3" t="n">
-        <v>3616</v>
+        <v>5561</v>
       </c>
       <c r="D3" t="n">
-        <v>18168</v>
+        <v>13821</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3897</v>
+        <v>3099</v>
       </c>
       <c r="C4" t="n">
-        <v>7184</v>
+        <v>8550</v>
       </c>
       <c r="D4" t="n">
-        <v>13894</v>
+        <v>11227</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2605</v>
+        <v>2078</v>
       </c>
       <c r="C5" t="n">
-        <v>8394</v>
+        <v>9286</v>
       </c>
       <c r="D5" t="n">
-        <v>6386</v>
+        <v>4993</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1262</v>
+        <v>1016</v>
       </c>
       <c r="C6" t="n">
-        <v>5999</v>
+        <v>7022</v>
       </c>
       <c r="D6" t="n">
-        <v>1967</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>3113</v>
+        <v>4289</v>
       </c>
       <c r="D7" t="n">
-        <v>708</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1340</v>
+        <v>2115</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>451</v>
+        <v>656</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3077</v>
+        <v>2216</v>
       </c>
       <c r="C2" t="n">
-        <v>2960</v>
+        <v>4550</v>
       </c>
       <c r="D2" t="n">
-        <v>10487</v>
+        <v>10908</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3278</v>
+        <v>2566</v>
       </c>
       <c r="C3" t="n">
-        <v>3729</v>
+        <v>5279</v>
       </c>
       <c r="D3" t="n">
-        <v>16929</v>
+        <v>13071</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3485</v>
+        <v>2757</v>
       </c>
       <c r="C4" t="n">
-        <v>5802</v>
+        <v>7388</v>
       </c>
       <c r="D4" t="n">
-        <v>14138</v>
+        <v>11317</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2848</v>
+        <v>2263</v>
       </c>
       <c r="C5" t="n">
-        <v>8111</v>
+        <v>9195</v>
       </c>
       <c r="D5" t="n">
-        <v>7046</v>
+        <v>5595</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1481</v>
+        <v>1176</v>
       </c>
       <c r="C6" t="n">
-        <v>6966</v>
+        <v>7973</v>
       </c>
       <c r="D6" t="n">
-        <v>2383</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>259</v>
       </c>
       <c r="C7" t="n">
-        <v>4004</v>
+        <v>5197</v>
       </c>
       <c r="D7" t="n">
-        <v>795</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1740</v>
+        <v>2637</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>516</v>
+        <v>716</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4136</v>
+        <v>3086</v>
       </c>
       <c r="C2" t="n">
-        <v>12314</v>
+        <v>8994</v>
       </c>
       <c r="D2" t="n">
-        <v>18990</v>
+        <v>18651</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2701</v>
+        <v>2063</v>
       </c>
       <c r="C3" t="n">
-        <v>3046</v>
+        <v>4468</v>
       </c>
       <c r="D3" t="n">
-        <v>15072</v>
+        <v>12013</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2966</v>
+        <v>2340</v>
       </c>
       <c r="C4" t="n">
-        <v>4805</v>
+        <v>6383</v>
       </c>
       <c r="D4" t="n">
-        <v>14110</v>
+        <v>11208</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2795</v>
+        <v>2236</v>
       </c>
       <c r="C5" t="n">
-        <v>7011</v>
+        <v>8309</v>
       </c>
       <c r="D5" t="n">
-        <v>7784</v>
+        <v>6085</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1801</v>
+        <v>1399</v>
       </c>
       <c r="C6" t="n">
-        <v>7347</v>
+        <v>8355</v>
       </c>
       <c r="D6" t="n">
-        <v>2934</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>607</v>
+        <v>475</v>
       </c>
       <c r="C7" t="n">
-        <v>5144</v>
+        <v>6174</v>
       </c>
       <c r="D7" t="n">
-        <v>973</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>2515</v>
+        <v>3514</v>
       </c>
       <c r="D8" t="n">
-        <v>450</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>916</v>
+        <v>1299</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>365</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6500</v>
+        <v>6244</v>
       </c>
       <c r="C2" t="n">
-        <v>3455</v>
+        <v>11695</v>
       </c>
       <c r="D2" t="n">
-        <v>14995</v>
+        <v>6355</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2994</v>
+        <v>2255</v>
       </c>
       <c r="C2" t="n">
-        <v>7092</v>
+        <v>5324</v>
       </c>
       <c r="D2" t="n">
-        <v>14128</v>
+        <v>13876</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3592</v>
+        <v>2757</v>
       </c>
       <c r="C3" t="n">
-        <v>5390</v>
+        <v>5878</v>
       </c>
       <c r="D3" t="n">
-        <v>16480</v>
+        <v>13437</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4097</v>
+        <v>3261</v>
       </c>
       <c r="C4" t="n">
-        <v>7126</v>
+        <v>9201</v>
       </c>
       <c r="D4" t="n">
-        <v>14465</v>
+        <v>11359</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1715</v>
+        <v>1313</v>
       </c>
       <c r="C5" t="n">
-        <v>10341</v>
+        <v>11898</v>
       </c>
       <c r="D5" t="n">
-        <v>7042</v>
+        <v>5525</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>560</v>
+        <v>438</v>
       </c>
       <c r="C6" t="n">
-        <v>6409</v>
+        <v>7524</v>
       </c>
       <c r="D6" t="n">
-        <v>2267</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>2464</v>
+        <v>3443</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>897</v>
+        <v>1273</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7583</v>
+        <v>7316</v>
       </c>
       <c r="C2" t="n">
-        <v>4806</v>
+        <v>11443</v>
       </c>
       <c r="D2" t="n">
-        <v>17128</v>
+        <v>15315</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2761</v>
+        <v>2653</v>
       </c>
       <c r="C3" t="n">
-        <v>1741</v>
+        <v>5894</v>
       </c>
       <c r="D3" t="n">
-        <v>3158</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4911</v>
+        <v>4395</v>
       </c>
       <c r="C2" t="n">
-        <v>5229</v>
+        <v>6707</v>
       </c>
       <c r="D2" t="n">
-        <v>28968</v>
+        <v>17584</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4246</v>
+        <v>4092</v>
       </c>
       <c r="C3" t="n">
-        <v>2997</v>
+        <v>7790</v>
       </c>
       <c r="D3" t="n">
-        <v>5272</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1233</v>
+        <v>1187</v>
       </c>
       <c r="C4" t="n">
-        <v>1064</v>
+        <v>3497</v>
       </c>
       <c r="D4" t="n">
-        <v>1817</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5421</v>
+        <v>5598</v>
       </c>
       <c r="C2" t="n">
-        <v>7732</v>
+        <v>6411</v>
       </c>
       <c r="D2" t="n">
-        <v>37344</v>
+        <v>25448</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3770</v>
+        <v>3535</v>
       </c>
       <c r="C3" t="n">
-        <v>3647</v>
+        <v>6252</v>
       </c>
       <c r="D3" t="n">
-        <v>8683</v>
+        <v>5782</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2318</v>
+        <v>2209</v>
       </c>
       <c r="C4" t="n">
-        <v>2136</v>
+        <v>5814</v>
       </c>
       <c r="D4" t="n">
-        <v>2425</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>567</v>
+        <v>538</v>
       </c>
       <c r="C5" t="n">
-        <v>677</v>
+        <v>1976</v>
       </c>
       <c r="D5" t="n">
-        <v>1253</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
@@ -5336,7 +5336,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6581</v>
+        <v>5315</v>
       </c>
       <c r="C2" t="n">
-        <v>6741</v>
+        <v>6550</v>
       </c>
       <c r="D2" t="n">
-        <v>34948</v>
+        <v>30222</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3740</v>
+        <v>3686</v>
       </c>
       <c r="C3" t="n">
-        <v>5004</v>
+        <v>5521</v>
       </c>
       <c r="D3" t="n">
-        <v>12428</v>
+        <v>8364</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2595</v>
+        <v>2439</v>
       </c>
       <c r="C4" t="n">
-        <v>2903</v>
+        <v>5924</v>
       </c>
       <c r="D4" t="n">
-        <v>3492</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1182</v>
+        <v>1111</v>
       </c>
       <c r="C5" t="n">
-        <v>1412</v>
+        <v>3868</v>
       </c>
       <c r="D5" t="n">
-        <v>1405</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="C6" t="n">
-        <v>488</v>
+        <v>1135</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8193</v>
+        <v>6742</v>
       </c>
       <c r="C2" t="n">
-        <v>5265</v>
+        <v>7161</v>
       </c>
       <c r="D2" t="n">
-        <v>30454</v>
+        <v>29322</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3715</v>
+        <v>3241</v>
       </c>
       <c r="C3" t="n">
-        <v>4826</v>
+        <v>4996</v>
       </c>
       <c r="D3" t="n">
-        <v>14089</v>
+        <v>10274</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1954</v>
+        <v>1876</v>
       </c>
       <c r="C4" t="n">
-        <v>3326</v>
+        <v>4620</v>
       </c>
       <c r="D4" t="n">
-        <v>4379</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>991</v>
+        <v>924</v>
       </c>
       <c r="C5" t="n">
-        <v>1588</v>
+        <v>3582</v>
       </c>
       <c r="D5" t="n">
-        <v>1384</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="C6" t="n">
-        <v>642</v>
+        <v>1647</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>266</v>
+        <v>465</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7020</v>
+        <v>5440</v>
       </c>
       <c r="C2" t="n">
-        <v>5051</v>
+        <v>8495</v>
       </c>
       <c r="D2" t="n">
-        <v>24561</v>
+        <v>24485</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4961</v>
+        <v>4157</v>
       </c>
       <c r="C3" t="n">
-        <v>4367</v>
+        <v>5374</v>
       </c>
       <c r="D3" t="n">
-        <v>15801</v>
+        <v>12717</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2493</v>
+        <v>2207</v>
       </c>
       <c r="C4" t="n">
-        <v>4164</v>
+        <v>4747</v>
       </c>
       <c r="D4" t="n">
-        <v>6161</v>
+        <v>4393</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1306</v>
+        <v>1243</v>
       </c>
       <c r="C5" t="n">
-        <v>2557</v>
+        <v>4105</v>
       </c>
       <c r="D5" t="n">
-        <v>1945</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>625</v>
+        <v>568</v>
       </c>
       <c r="C6" t="n">
-        <v>1178</v>
+        <v>2704</v>
       </c>
       <c r="D6" t="n">
-        <v>883</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>479</v>
+        <v>1113</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>246</v>
+        <v>347</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6492</v>
+        <v>4906</v>
       </c>
       <c r="C2" t="n">
-        <v>10120</v>
+        <v>7905</v>
       </c>
       <c r="D2" t="n">
-        <v>20807</v>
+        <v>27125</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4907</v>
+        <v>3930</v>
       </c>
       <c r="C3" t="n">
-        <v>4102</v>
+        <v>6092</v>
       </c>
       <c r="D3" t="n">
-        <v>16064</v>
+        <v>13610</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3175</v>
+        <v>2715</v>
       </c>
       <c r="C4" t="n">
-        <v>4192</v>
+        <v>4991</v>
       </c>
       <c r="D4" t="n">
-        <v>7824</v>
+        <v>5735</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1671</v>
+        <v>1496</v>
       </c>
       <c r="C5" t="n">
-        <v>3358</v>
+        <v>4319</v>
       </c>
       <c r="D5" t="n">
-        <v>2636</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>872</v>
+        <v>815</v>
       </c>
       <c r="C6" t="n">
-        <v>1905</v>
+        <v>3399</v>
       </c>
       <c r="D6" t="n">
-        <v>1064</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>366</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>848</v>
+        <v>1923</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>364</v>
+        <v>718</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>225</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_97_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6549</v>
+        <v>5804</v>
       </c>
       <c r="C2" t="n">
-        <v>9192</v>
+        <v>10290</v>
       </c>
       <c r="D2" t="n">
-        <v>23795</v>
+        <v>38690</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3601</v>
+        <v>3371</v>
       </c>
       <c r="C3" t="n">
-        <v>6158</v>
+        <v>8245</v>
       </c>
       <c r="D3" t="n">
-        <v>14619</v>
+        <v>18493</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2814</v>
+        <v>2454</v>
       </c>
       <c r="C4" t="n">
-        <v>5388</v>
+        <v>8342</v>
       </c>
       <c r="D4" t="n">
-        <v>6921</v>
+        <v>8501</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1787</v>
+        <v>1625</v>
       </c>
       <c r="C5" t="n">
-        <v>4558</v>
+        <v>5560</v>
       </c>
       <c r="D5" t="n">
-        <v>2509</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1018</v>
+        <v>966</v>
       </c>
       <c r="C6" t="n">
-        <v>3763</v>
+        <v>2690</v>
       </c>
       <c r="D6" t="n">
-        <v>1080</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="C7" t="n">
-        <v>2616</v>
+        <v>1488</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>675</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C8" t="n">
-        <v>1253</v>
+        <v>743</v>
       </c>
       <c r="D8" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>470</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6856</v>
+        <v>6022</v>
       </c>
       <c r="C2" t="n">
-        <v>14037</v>
+        <v>18616</v>
       </c>
       <c r="D2" t="n">
-        <v>29108</v>
+        <v>40030</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3936</v>
+        <v>3580</v>
       </c>
       <c r="C3" t="n">
-        <v>6603</v>
+        <v>8067</v>
       </c>
       <c r="D3" t="n">
-        <v>14834</v>
+        <v>19865</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2689</v>
+        <v>2424</v>
       </c>
       <c r="C4" t="n">
-        <v>5630</v>
+        <v>8043</v>
       </c>
       <c r="D4" t="n">
-        <v>7826</v>
+        <v>9695</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1975</v>
+        <v>1746</v>
       </c>
       <c r="C5" t="n">
-        <v>4785</v>
+        <v>6699</v>
       </c>
       <c r="D5" t="n">
-        <v>3110</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1212</v>
+        <v>1141</v>
       </c>
       <c r="C6" t="n">
-        <v>4034</v>
+        <v>3878</v>
       </c>
       <c r="D6" t="n">
-        <v>1260</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>631</v>
+        <v>596</v>
       </c>
       <c r="C7" t="n">
-        <v>3109</v>
+        <v>1991</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>1801</v>
+        <v>1056</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>784</v>
+        <v>495</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>259</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7346</v>
+        <v>6866</v>
       </c>
       <c r="C2" t="n">
-        <v>14268</v>
+        <v>15479</v>
       </c>
       <c r="D2" t="n">
-        <v>26527</v>
+        <v>50654</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4120</v>
+        <v>3686</v>
       </c>
       <c r="C3" t="n">
-        <v>8441</v>
+        <v>10818</v>
       </c>
       <c r="D3" t="n">
-        <v>15597</v>
+        <v>21013</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2696</v>
+        <v>2440</v>
       </c>
       <c r="C4" t="n">
-        <v>5860</v>
+        <v>7808</v>
       </c>
       <c r="D4" t="n">
-        <v>8597</v>
+        <v>10864</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2006</v>
+        <v>1787</v>
       </c>
       <c r="C5" t="n">
-        <v>4980</v>
+        <v>7037</v>
       </c>
       <c r="D5" t="n">
-        <v>3619</v>
+        <v>4554</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1370</v>
+        <v>1254</v>
       </c>
       <c r="C6" t="n">
-        <v>4294</v>
+        <v>4916</v>
       </c>
       <c r="D6" t="n">
-        <v>1492</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>766</v>
+        <v>722</v>
       </c>
       <c r="C7" t="n">
-        <v>3430</v>
+        <v>2729</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="C8" t="n">
-        <v>2269</v>
+        <v>1393</v>
       </c>
       <c r="D8" t="n">
-        <v>470</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>1144</v>
+        <v>693</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>480</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6832</v>
+        <v>6379</v>
       </c>
       <c r="C2" t="n">
-        <v>9930</v>
+        <v>10897</v>
       </c>
       <c r="D2" t="n">
-        <v>21970</v>
+        <v>41531</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4859</v>
+        <v>4340</v>
       </c>
       <c r="C3" t="n">
-        <v>12118</v>
+        <v>15244</v>
       </c>
       <c r="D3" t="n">
-        <v>16865</v>
+        <v>22501</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1853</v>
+        <v>1651</v>
       </c>
       <c r="C4" t="n">
-        <v>7874</v>
+        <v>10878</v>
       </c>
       <c r="D4" t="n">
-        <v>8113</v>
+        <v>10283</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1265</v>
+        <v>1158</v>
       </c>
       <c r="C5" t="n">
-        <v>4208</v>
+        <v>4817</v>
       </c>
       <c r="D5" t="n">
-        <v>2434</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>707</v>
+        <v>667</v>
       </c>
       <c r="C6" t="n">
-        <v>3361</v>
+        <v>2674</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>830</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C7" t="n">
-        <v>2223</v>
+        <v>1365</v>
       </c>
       <c r="D7" t="n">
-        <v>460</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>1121</v>
+        <v>679</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>470</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4098</v>
+        <v>3858</v>
       </c>
       <c r="C2" t="n">
-        <v>5335</v>
+        <v>4813</v>
       </c>
       <c r="D2" t="n">
-        <v>15450</v>
+        <v>29533</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4905</v>
+        <v>4504</v>
       </c>
       <c r="C3" t="n">
-        <v>10137</v>
+        <v>12174</v>
       </c>
       <c r="D3" t="n">
-        <v>16749</v>
+        <v>23676</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2566</v>
+        <v>2266</v>
       </c>
       <c r="C4" t="n">
-        <v>9927</v>
+        <v>12893</v>
       </c>
       <c r="D4" t="n">
-        <v>9282</v>
+        <v>11927</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1407</v>
+        <v>1265</v>
       </c>
       <c r="C5" t="n">
-        <v>5765</v>
+        <v>7333</v>
       </c>
       <c r="D5" t="n">
-        <v>3060</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>833</v>
+        <v>782</v>
       </c>
       <c r="C6" t="n">
-        <v>3810</v>
+        <v>3511</v>
       </c>
       <c r="D6" t="n">
-        <v>896</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="C7" t="n">
-        <v>2708</v>
+        <v>1818</v>
       </c>
       <c r="D7" t="n">
-        <v>499</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>1444</v>
+        <v>882</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>505</v>
+        <v>370</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>165</v>
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4189</v>
+        <v>3799</v>
       </c>
       <c r="C2" t="n">
-        <v>9200</v>
+        <v>3976</v>
       </c>
       <c r="D2" t="n">
-        <v>16987</v>
+        <v>25758</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3851</v>
+        <v>3575</v>
       </c>
       <c r="C3" t="n">
-        <v>7097</v>
+        <v>7963</v>
       </c>
       <c r="D3" t="n">
-        <v>15446</v>
+        <v>23108</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3048</v>
+        <v>2712</v>
       </c>
       <c r="C4" t="n">
-        <v>9819</v>
+        <v>12293</v>
       </c>
       <c r="D4" t="n">
-        <v>10218</v>
+        <v>13369</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1666</v>
+        <v>1485</v>
       </c>
       <c r="C5" t="n">
-        <v>7522</v>
+        <v>9635</v>
       </c>
       <c r="D5" t="n">
-        <v>3922</v>
+        <v>4821</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>973</v>
+        <v>903</v>
       </c>
       <c r="C6" t="n">
-        <v>4656</v>
+        <v>5127</v>
       </c>
       <c r="D6" t="n">
-        <v>1195</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="C7" t="n">
-        <v>3160</v>
+        <v>2497</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>1953</v>
+        <v>1248</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>855</v>
+        <v>554</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2543</v>
+        <v>2327</v>
       </c>
       <c r="C2" t="n">
-        <v>4446</v>
+        <v>1985</v>
       </c>
       <c r="D2" t="n">
-        <v>11846</v>
+        <v>18215</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3792</v>
+        <v>3501</v>
       </c>
       <c r="C3" t="n">
-        <v>7576</v>
+        <v>6515</v>
       </c>
       <c r="D3" t="n">
-        <v>15260</v>
+        <v>22881</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3329</v>
+        <v>2961</v>
       </c>
       <c r="C4" t="n">
-        <v>9721</v>
+        <v>11928</v>
       </c>
       <c r="D4" t="n">
-        <v>10887</v>
+        <v>14444</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1722</v>
+        <v>1540</v>
       </c>
       <c r="C5" t="n">
-        <v>9136</v>
+        <v>11708</v>
       </c>
       <c r="D5" t="n">
-        <v>4150</v>
+        <v>4958</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>788</v>
+        <v>731</v>
       </c>
       <c r="C6" t="n">
-        <v>5585</v>
+        <v>5663</v>
       </c>
       <c r="D6" t="n">
-        <v>1176</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>3383</v>
+        <v>2471</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1412</v>
+        <v>885</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>314</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3178</v>
+        <v>3090</v>
       </c>
       <c r="C2" t="n">
-        <v>6035</v>
+        <v>11739</v>
       </c>
       <c r="D2" t="n">
-        <v>13641</v>
+        <v>15629</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2816</v>
+        <v>2616</v>
       </c>
       <c r="C3" t="n">
-        <v>5561</v>
+        <v>4123</v>
       </c>
       <c r="D3" t="n">
-        <v>13821</v>
+        <v>21002</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3099</v>
+        <v>2764</v>
       </c>
       <c r="C4" t="n">
-        <v>8550</v>
+        <v>9404</v>
       </c>
       <c r="D4" t="n">
-        <v>11227</v>
+        <v>15219</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2078</v>
+        <v>1842</v>
       </c>
       <c r="C5" t="n">
-        <v>9286</v>
+        <v>11555</v>
       </c>
       <c r="D5" t="n">
-        <v>4993</v>
+        <v>6082</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1016</v>
+        <v>925</v>
       </c>
       <c r="C6" t="n">
-        <v>7022</v>
+        <v>8104</v>
       </c>
       <c r="D6" t="n">
-        <v>1571</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="C7" t="n">
-        <v>4289</v>
+        <v>3651</v>
       </c>
       <c r="D7" t="n">
-        <v>621</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2115</v>
+        <v>1430</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>656</v>
+        <v>455</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3103,7 +3103,7 @@
         <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2216</v>
+        <v>1979</v>
       </c>
       <c r="C2" t="n">
-        <v>4550</v>
+        <v>6388</v>
       </c>
       <c r="D2" t="n">
-        <v>10908</v>
+        <v>11667</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2566</v>
+        <v>2418</v>
       </c>
       <c r="C3" t="n">
-        <v>5279</v>
+        <v>6304</v>
       </c>
       <c r="D3" t="n">
-        <v>13071</v>
+        <v>19492</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2757</v>
+        <v>2509</v>
       </c>
       <c r="C4" t="n">
-        <v>7388</v>
+        <v>7462</v>
       </c>
       <c r="D4" t="n">
-        <v>11317</v>
+        <v>15568</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2263</v>
+        <v>1979</v>
       </c>
       <c r="C5" t="n">
-        <v>9195</v>
+        <v>11056</v>
       </c>
       <c r="D5" t="n">
-        <v>5595</v>
+        <v>6832</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1176</v>
+        <v>1051</v>
       </c>
       <c r="C6" t="n">
-        <v>7973</v>
+        <v>9380</v>
       </c>
       <c r="D6" t="n">
-        <v>1846</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="C7" t="n">
-        <v>5197</v>
+        <v>4780</v>
       </c>
       <c r="D7" t="n">
-        <v>690</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>2637</v>
+        <v>1888</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>716</v>
+        <v>474</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3086</v>
+        <v>2484</v>
       </c>
       <c r="C2" t="n">
-        <v>8994</v>
+        <v>12250</v>
       </c>
       <c r="D2" t="n">
-        <v>18651</v>
+        <v>14686</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2063</v>
+        <v>1923</v>
       </c>
       <c r="C3" t="n">
-        <v>4468</v>
+        <v>5726</v>
       </c>
       <c r="D3" t="n">
-        <v>12013</v>
+        <v>17399</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2340</v>
+        <v>2155</v>
       </c>
       <c r="C4" t="n">
-        <v>6383</v>
+        <v>6862</v>
       </c>
       <c r="D4" t="n">
-        <v>11208</v>
+        <v>15622</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2236</v>
+        <v>1957</v>
       </c>
       <c r="C5" t="n">
-        <v>8309</v>
+        <v>9408</v>
       </c>
       <c r="D5" t="n">
-        <v>6085</v>
+        <v>7714</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1399</v>
+        <v>1240</v>
       </c>
       <c r="C6" t="n">
-        <v>8355</v>
+        <v>9994</v>
       </c>
       <c r="D6" t="n">
-        <v>2290</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>475</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>6174</v>
+        <v>6310</v>
       </c>
       <c r="D7" t="n">
-        <v>818</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>3514</v>
+        <v>2794</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1299</v>
+        <v>894</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>365</v>
+        <v>281</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6244</v>
+        <v>4936</v>
       </c>
       <c r="C2" t="n">
-        <v>11695</v>
+        <v>5425</v>
       </c>
       <c r="D2" t="n">
-        <v>6355</v>
+        <v>17783</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2255</v>
+        <v>1854</v>
       </c>
       <c r="C2" t="n">
-        <v>5324</v>
+        <v>7448</v>
       </c>
       <c r="D2" t="n">
-        <v>13876</v>
+        <v>11043</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2757</v>
+        <v>2530</v>
       </c>
       <c r="C3" t="n">
-        <v>5878</v>
+        <v>7716</v>
       </c>
       <c r="D3" t="n">
-        <v>13437</v>
+        <v>18607</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3261</v>
+        <v>2891</v>
       </c>
       <c r="C4" t="n">
-        <v>9201</v>
+        <v>9971</v>
       </c>
       <c r="D4" t="n">
-        <v>11359</v>
+        <v>15722</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1313</v>
+        <v>1145</v>
       </c>
       <c r="C5" t="n">
-        <v>11898</v>
+        <v>14007</v>
       </c>
       <c r="D5" t="n">
-        <v>5525</v>
+        <v>6814</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>438</v>
+        <v>377</v>
       </c>
       <c r="C6" t="n">
-        <v>7524</v>
+        <v>7750</v>
       </c>
       <c r="D6" t="n">
-        <v>1805</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>3443</v>
+        <v>2738</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1273</v>
+        <v>876</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>357</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7316</v>
+        <v>7191</v>
       </c>
       <c r="C2" t="n">
-        <v>11443</v>
+        <v>6488</v>
       </c>
       <c r="D2" t="n">
-        <v>15315</v>
+        <v>19882</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2653</v>
+        <v>2098</v>
       </c>
       <c r="C3" t="n">
-        <v>5894</v>
+        <v>2734</v>
       </c>
       <c r="D3" t="n">
-        <v>1706</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4395</v>
+        <v>4541</v>
       </c>
       <c r="C2" t="n">
-        <v>6707</v>
+        <v>3827</v>
       </c>
       <c r="D2" t="n">
-        <v>17584</v>
+        <v>28039</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4092</v>
+        <v>3809</v>
       </c>
       <c r="C3" t="n">
-        <v>7790</v>
+        <v>4189</v>
       </c>
       <c r="D3" t="n">
-        <v>3866</v>
+        <v>6090</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1187</v>
+        <v>945</v>
       </c>
       <c r="C4" t="n">
-        <v>3497</v>
+        <v>1647</v>
       </c>
       <c r="D4" t="n">
-        <v>1525</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5598</v>
+        <v>4730</v>
       </c>
       <c r="C2" t="n">
-        <v>6411</v>
+        <v>4723</v>
       </c>
       <c r="D2" t="n">
-        <v>25448</v>
+        <v>21392</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3535</v>
+        <v>3435</v>
       </c>
       <c r="C3" t="n">
-        <v>6252</v>
+        <v>3455</v>
       </c>
       <c r="D3" t="n">
-        <v>5782</v>
+        <v>9163</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2209</v>
+        <v>2016</v>
       </c>
       <c r="C4" t="n">
-        <v>5814</v>
+        <v>3052</v>
       </c>
       <c r="D4" t="n">
-        <v>1928</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>538</v>
+        <v>440</v>
       </c>
       <c r="C5" t="n">
-        <v>1976</v>
+        <v>996</v>
       </c>
       <c r="D5" t="n">
-        <v>1209</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5315</v>
+        <v>4565</v>
       </c>
       <c r="C2" t="n">
-        <v>6550</v>
+        <v>10984</v>
       </c>
       <c r="D2" t="n">
-        <v>30222</v>
+        <v>25747</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3686</v>
+        <v>3329</v>
       </c>
       <c r="C3" t="n">
-        <v>5521</v>
+        <v>3575</v>
       </c>
       <c r="D3" t="n">
-        <v>8364</v>
+        <v>10376</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2439</v>
+        <v>2320</v>
       </c>
       <c r="C4" t="n">
-        <v>5924</v>
+        <v>3205</v>
       </c>
       <c r="D4" t="n">
-        <v>2572</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1111</v>
+        <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>3868</v>
+        <v>2031</v>
       </c>
       <c r="D5" t="n">
-        <v>1284</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>1135</v>
+        <v>653</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
         <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
         <v>158</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6742</v>
+        <v>5732</v>
       </c>
       <c r="C2" t="n">
-        <v>7161</v>
+        <v>16249</v>
       </c>
       <c r="D2" t="n">
-        <v>29322</v>
+        <v>33489</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3241</v>
+        <v>2861</v>
       </c>
       <c r="C3" t="n">
-        <v>4996</v>
+        <v>6030</v>
       </c>
       <c r="D3" t="n">
-        <v>10274</v>
+        <v>11273</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1876</v>
+        <v>1742</v>
       </c>
       <c r="C4" t="n">
-        <v>4620</v>
+        <v>2768</v>
       </c>
       <c r="D4" t="n">
-        <v>3024</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>924</v>
+        <v>868</v>
       </c>
       <c r="C5" t="n">
-        <v>3582</v>
+        <v>1937</v>
       </c>
       <c r="D5" t="n">
-        <v>1188</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>324</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
-        <v>1647</v>
+        <v>907</v>
       </c>
       <c r="D6" t="n">
-        <v>754</v>
+        <v>795</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>465</v>
+        <v>317</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
         <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5440</v>
+        <v>4793</v>
       </c>
       <c r="C2" t="n">
-        <v>8495</v>
+        <v>11362</v>
       </c>
       <c r="D2" t="n">
-        <v>24485</v>
+        <v>40591</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4157</v>
+        <v>3576</v>
       </c>
       <c r="C3" t="n">
-        <v>5374</v>
+        <v>10331</v>
       </c>
       <c r="D3" t="n">
-        <v>12717</v>
+        <v>14175</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2207</v>
+        <v>2019</v>
       </c>
       <c r="C4" t="n">
-        <v>4747</v>
+        <v>4683</v>
       </c>
       <c r="D4" t="n">
-        <v>4393</v>
+        <v>5483</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1243</v>
+        <v>1165</v>
       </c>
       <c r="C5" t="n">
-        <v>4105</v>
+        <v>2383</v>
       </c>
       <c r="D5" t="n">
-        <v>1492</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>568</v>
+        <v>534</v>
       </c>
       <c r="C6" t="n">
-        <v>2704</v>
+        <v>1470</v>
       </c>
       <c r="D6" t="n">
-        <v>826</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>1113</v>
+        <v>652</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>347</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4906</v>
+        <v>4818</v>
       </c>
       <c r="C2" t="n">
-        <v>7905</v>
+        <v>9404</v>
       </c>
       <c r="D2" t="n">
-        <v>27125</v>
+        <v>33415</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3930</v>
+        <v>3432</v>
       </c>
       <c r="C3" t="n">
-        <v>6092</v>
+        <v>9437</v>
       </c>
       <c r="D3" t="n">
-        <v>13610</v>
+        <v>17380</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2715</v>
+        <v>2404</v>
       </c>
       <c r="C4" t="n">
-        <v>4991</v>
+        <v>7685</v>
       </c>
       <c r="D4" t="n">
-        <v>5735</v>
+        <v>6985</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1496</v>
+        <v>1389</v>
       </c>
       <c r="C5" t="n">
-        <v>4319</v>
+        <v>3591</v>
       </c>
       <c r="D5" t="n">
-        <v>1975</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>815</v>
+        <v>771</v>
       </c>
       <c r="C6" t="n">
-        <v>3399</v>
+        <v>1935</v>
       </c>
       <c r="D6" t="n">
-        <v>921</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>1923</v>
+        <v>1076</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>718</v>
+        <v>460</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_97_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_97_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5804</v>
+        <v>1649</v>
       </c>
       <c r="C2" t="n">
-        <v>10290</v>
+        <v>2691</v>
       </c>
       <c r="D2" t="n">
-        <v>38690</v>
+        <v>15029</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3371</v>
+        <v>2661</v>
       </c>
       <c r="C3" t="n">
-        <v>8245</v>
+        <v>6180</v>
       </c>
       <c r="D3" t="n">
-        <v>18493</v>
+        <v>14769</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2454</v>
+        <v>1693</v>
       </c>
       <c r="C4" t="n">
-        <v>8342</v>
+        <v>6732</v>
       </c>
       <c r="D4" t="n">
-        <v>8501</v>
+        <v>6456</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1625</v>
+        <v>851</v>
       </c>
       <c r="C5" t="n">
-        <v>5560</v>
+        <v>3837</v>
       </c>
       <c r="D5" t="n">
-        <v>3226</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>966</v>
+        <v>329</v>
       </c>
       <c r="C6" t="n">
-        <v>2690</v>
+        <v>1554</v>
       </c>
       <c r="D6" t="n">
-        <v>1312</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>458</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>1488</v>
+        <v>602</v>
       </c>
       <c r="D7" t="n">
-        <v>675</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>743</v>
+        <v>342</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6022</v>
+        <v>2264</v>
       </c>
       <c r="C2" t="n">
-        <v>18616</v>
+        <v>12243</v>
       </c>
       <c r="D2" t="n">
-        <v>40030</v>
+        <v>16577</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3580</v>
+        <v>1834</v>
       </c>
       <c r="C3" t="n">
-        <v>8067</v>
+        <v>3740</v>
       </c>
       <c r="D3" t="n">
-        <v>19865</v>
+        <v>13889</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2424</v>
+        <v>1873</v>
       </c>
       <c r="C4" t="n">
-        <v>8043</v>
+        <v>6349</v>
       </c>
       <c r="D4" t="n">
-        <v>9695</v>
+        <v>7776</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1746</v>
+        <v>1098</v>
       </c>
       <c r="C5" t="n">
-        <v>6699</v>
+        <v>5285</v>
       </c>
       <c r="D5" t="n">
-        <v>3938</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1141</v>
+        <v>513</v>
       </c>
       <c r="C6" t="n">
-        <v>3878</v>
+        <v>2713</v>
       </c>
       <c r="D6" t="n">
-        <v>1557</v>
+        <v>952</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>596</v>
+        <v>176</v>
       </c>
       <c r="C7" t="n">
-        <v>1991</v>
+        <v>1074</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1056</v>
+        <v>468</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>495</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6866</v>
+        <v>1183</v>
       </c>
       <c r="C2" t="n">
-        <v>15479</v>
+        <v>5035</v>
       </c>
       <c r="D2" t="n">
-        <v>50654</v>
+        <v>11202</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3686</v>
+        <v>1883</v>
       </c>
       <c r="C3" t="n">
-        <v>10818</v>
+        <v>6881</v>
       </c>
       <c r="D3" t="n">
-        <v>21013</v>
+        <v>13855</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2440</v>
+        <v>2060</v>
       </c>
       <c r="C4" t="n">
-        <v>7808</v>
+        <v>5835</v>
       </c>
       <c r="D4" t="n">
-        <v>10864</v>
+        <v>8617</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1787</v>
+        <v>1104</v>
       </c>
       <c r="C5" t="n">
-        <v>7037</v>
+        <v>6232</v>
       </c>
       <c r="D5" t="n">
-        <v>4554</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1254</v>
+        <v>393</v>
       </c>
       <c r="C6" t="n">
-        <v>4916</v>
+        <v>3541</v>
       </c>
       <c r="D6" t="n">
-        <v>1856</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>722</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2729</v>
+        <v>1067</v>
       </c>
       <c r="D7" t="n">
-        <v>847</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>339</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1393</v>
+        <v>475</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>693</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6379</v>
+        <v>1074</v>
       </c>
       <c r="C2" t="n">
-        <v>10897</v>
+        <v>4311</v>
       </c>
       <c r="D2" t="n">
-        <v>41531</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4340</v>
+        <v>1317</v>
       </c>
       <c r="C3" t="n">
-        <v>15244</v>
+        <v>5202</v>
       </c>
       <c r="D3" t="n">
-        <v>22501</v>
+        <v>12476</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1651</v>
+        <v>1757</v>
       </c>
       <c r="C4" t="n">
-        <v>10878</v>
+        <v>6331</v>
       </c>
       <c r="D4" t="n">
-        <v>10283</v>
+        <v>9393</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1158</v>
+        <v>1372</v>
       </c>
       <c r="C5" t="n">
-        <v>4817</v>
+        <v>5960</v>
       </c>
       <c r="D5" t="n">
-        <v>2999</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>667</v>
+        <v>617</v>
       </c>
       <c r="C6" t="n">
-        <v>2674</v>
+        <v>4865</v>
       </c>
       <c r="D6" t="n">
-        <v>830</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>313</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>1365</v>
+        <v>2202</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>679</v>
+        <v>732</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3858</v>
+        <v>697</v>
       </c>
       <c r="C2" t="n">
-        <v>4813</v>
+        <v>2158</v>
       </c>
       <c r="D2" t="n">
-        <v>29533</v>
+        <v>10320</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4504</v>
+        <v>1070</v>
       </c>
       <c r="C3" t="n">
-        <v>12174</v>
+        <v>4305</v>
       </c>
       <c r="D3" t="n">
-        <v>23676</v>
+        <v>11842</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2266</v>
+        <v>1481</v>
       </c>
       <c r="C4" t="n">
-        <v>12893</v>
+        <v>5850</v>
       </c>
       <c r="D4" t="n">
-        <v>11927</v>
+        <v>9671</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1265</v>
+        <v>1458</v>
       </c>
       <c r="C5" t="n">
-        <v>7333</v>
+        <v>6221</v>
       </c>
       <c r="D5" t="n">
-        <v>3804</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>782</v>
+        <v>774</v>
       </c>
       <c r="C6" t="n">
-        <v>3511</v>
+        <v>5511</v>
       </c>
       <c r="D6" t="n">
-        <v>1031</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>290</v>
+        <v>185</v>
       </c>
       <c r="C7" t="n">
-        <v>1818</v>
+        <v>3135</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>882</v>
+        <v>1098</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>370</v>
+        <v>434</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3799</v>
+        <v>840</v>
       </c>
       <c r="C2" t="n">
-        <v>3976</v>
+        <v>6119</v>
       </c>
       <c r="D2" t="n">
-        <v>25758</v>
+        <v>13465</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3575</v>
+        <v>772</v>
       </c>
       <c r="C3" t="n">
-        <v>7963</v>
+        <v>2905</v>
       </c>
       <c r="D3" t="n">
-        <v>23108</v>
+        <v>10839</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2712</v>
+        <v>1143</v>
       </c>
       <c r="C4" t="n">
-        <v>12293</v>
+        <v>4971</v>
       </c>
       <c r="D4" t="n">
-        <v>13369</v>
+        <v>9731</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>1354</v>
       </c>
       <c r="C5" t="n">
-        <v>9635</v>
+        <v>5976</v>
       </c>
       <c r="D5" t="n">
-        <v>4821</v>
+        <v>5289</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>903</v>
+        <v>964</v>
       </c>
       <c r="C6" t="n">
-        <v>5127</v>
+        <v>5771</v>
       </c>
       <c r="D6" t="n">
-        <v>1416</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>355</v>
       </c>
       <c r="C7" t="n">
-        <v>2497</v>
+        <v>4189</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>1248</v>
+        <v>1926</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>554</v>
+        <v>685</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2327</v>
+        <v>564</v>
       </c>
       <c r="C2" t="n">
-        <v>1985</v>
+        <v>3181</v>
       </c>
       <c r="D2" t="n">
-        <v>18215</v>
+        <v>9695</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3501</v>
+        <v>1076</v>
       </c>
       <c r="C3" t="n">
-        <v>6515</v>
+        <v>4028</v>
       </c>
       <c r="D3" t="n">
-        <v>22881</v>
+        <v>11949</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2961</v>
+        <v>1813</v>
       </c>
       <c r="C4" t="n">
-        <v>11928</v>
+        <v>6737</v>
       </c>
       <c r="D4" t="n">
-        <v>14444</v>
+        <v>10042</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1540</v>
+        <v>990</v>
       </c>
       <c r="C5" t="n">
-        <v>11708</v>
+        <v>8430</v>
       </c>
       <c r="D5" t="n">
-        <v>4958</v>
+        <v>4859</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>731</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>5663</v>
+        <v>5575</v>
       </c>
       <c r="D6" t="n">
-        <v>1371</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>2471</v>
+        <v>1887</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>885</v>
+        <v>671</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3090</v>
+        <v>408</v>
       </c>
       <c r="C2" t="n">
-        <v>11739</v>
+        <v>1787</v>
       </c>
       <c r="D2" t="n">
-        <v>15629</v>
+        <v>7286</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2616</v>
+        <v>727</v>
       </c>
       <c r="C3" t="n">
-        <v>4123</v>
+        <v>3181</v>
       </c>
       <c r="D3" t="n">
-        <v>21002</v>
+        <v>10767</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2764</v>
+        <v>1228</v>
       </c>
       <c r="C4" t="n">
-        <v>9404</v>
+        <v>5017</v>
       </c>
       <c r="D4" t="n">
-        <v>15219</v>
+        <v>9653</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1842</v>
+        <v>949</v>
       </c>
       <c r="C5" t="n">
-        <v>11555</v>
+        <v>6762</v>
       </c>
       <c r="D5" t="n">
-        <v>6082</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>925</v>
+        <v>338</v>
       </c>
       <c r="C6" t="n">
-        <v>8104</v>
+        <v>5635</v>
       </c>
       <c r="D6" t="n">
-        <v>1801</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>261</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>3651</v>
+        <v>2492</v>
       </c>
       <c r="D7" t="n">
-        <v>674</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1430</v>
+        <v>749</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>455</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1979</v>
+        <v>296</v>
       </c>
       <c r="C2" t="n">
-        <v>6388</v>
+        <v>4561</v>
       </c>
       <c r="D2" t="n">
-        <v>11667</v>
+        <v>11201</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2418</v>
+        <v>482</v>
       </c>
       <c r="C3" t="n">
-        <v>6304</v>
+        <v>2095</v>
       </c>
       <c r="D3" t="n">
-        <v>19492</v>
+        <v>9434</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2509</v>
+        <v>872</v>
       </c>
       <c r="C4" t="n">
-        <v>7462</v>
+        <v>3920</v>
       </c>
       <c r="D4" t="n">
-        <v>15568</v>
+        <v>9573</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1979</v>
+        <v>970</v>
       </c>
       <c r="C5" t="n">
-        <v>11056</v>
+        <v>5683</v>
       </c>
       <c r="D5" t="n">
-        <v>6832</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1051</v>
+        <v>564</v>
       </c>
       <c r="C6" t="n">
-        <v>9380</v>
+        <v>6211</v>
       </c>
       <c r="D6" t="n">
-        <v>2161</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>231</v>
+        <v>166</v>
       </c>
       <c r="C7" t="n">
-        <v>4780</v>
+        <v>4086</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>792</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>1888</v>
+        <v>1575</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2484</v>
+        <v>648</v>
       </c>
       <c r="C2" t="n">
-        <v>12250</v>
+        <v>10103</v>
       </c>
       <c r="D2" t="n">
-        <v>14686</v>
+        <v>12284</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1923</v>
+        <v>332</v>
       </c>
       <c r="C3" t="n">
-        <v>5726</v>
+        <v>2895</v>
       </c>
       <c r="D3" t="n">
-        <v>17399</v>
+        <v>9039</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2155</v>
+        <v>608</v>
       </c>
       <c r="C4" t="n">
-        <v>6862</v>
+        <v>2892</v>
       </c>
       <c r="D4" t="n">
-        <v>15622</v>
+        <v>9166</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1957</v>
+        <v>848</v>
       </c>
       <c r="C5" t="n">
-        <v>9408</v>
+        <v>4684</v>
       </c>
       <c r="D5" t="n">
-        <v>7714</v>
+        <v>6195</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1240</v>
+        <v>685</v>
       </c>
       <c r="C6" t="n">
-        <v>9994</v>
+        <v>5892</v>
       </c>
       <c r="D6" t="n">
-        <v>2671</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>299</v>
       </c>
       <c r="C7" t="n">
-        <v>6310</v>
+        <v>5083</v>
       </c>
       <c r="D7" t="n">
-        <v>890</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>2794</v>
+        <v>2706</v>
       </c>
       <c r="D8" t="n">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>894</v>
+        <v>954</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="D10" t="n">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4936</v>
+        <v>4362</v>
       </c>
       <c r="C2" t="n">
-        <v>5425</v>
+        <v>6823</v>
       </c>
       <c r="D2" t="n">
-        <v>17783</v>
+        <v>16796</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1854</v>
+        <v>1185</v>
       </c>
       <c r="C2" t="n">
-        <v>7448</v>
+        <v>12970</v>
       </c>
       <c r="D2" t="n">
-        <v>11043</v>
+        <v>25353</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2530</v>
+        <v>379</v>
       </c>
       <c r="C3" t="n">
-        <v>7716</v>
+        <v>5377</v>
       </c>
       <c r="D3" t="n">
-        <v>18607</v>
+        <v>8872</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2891</v>
+        <v>431</v>
       </c>
       <c r="C4" t="n">
-        <v>9971</v>
+        <v>2833</v>
       </c>
       <c r="D4" t="n">
-        <v>15722</v>
+        <v>8866</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1145</v>
+        <v>687</v>
       </c>
       <c r="C5" t="n">
-        <v>14007</v>
+        <v>3733</v>
       </c>
       <c r="D5" t="n">
-        <v>6814</v>
+        <v>6463</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>377</v>
+        <v>702</v>
       </c>
       <c r="C6" t="n">
-        <v>7750</v>
+        <v>5301</v>
       </c>
       <c r="D6" t="n">
-        <v>2050</v>
+        <v>3284</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>2738</v>
+        <v>5429</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>876</v>
+        <v>3656</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>275</v>
+        <v>1657</v>
       </c>
       <c r="D9" t="n">
-        <v>177</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>142</v>
+        <v>556</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7191</v>
+        <v>6834</v>
       </c>
       <c r="C2" t="n">
-        <v>6488</v>
+        <v>7841</v>
       </c>
       <c r="D2" t="n">
-        <v>19882</v>
+        <v>15276</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2098</v>
+        <v>1442</v>
       </c>
       <c r="C3" t="n">
-        <v>2734</v>
+        <v>2694</v>
       </c>
       <c r="D3" t="n">
-        <v>3626</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4541</v>
+        <v>3559</v>
       </c>
       <c r="C2" t="n">
-        <v>3827</v>
+        <v>4653</v>
       </c>
       <c r="D2" t="n">
-        <v>28039</v>
+        <v>19066</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3809</v>
+        <v>3517</v>
       </c>
       <c r="C3" t="n">
-        <v>4189</v>
+        <v>4982</v>
       </c>
       <c r="D3" t="n">
-        <v>6090</v>
+        <v>4860</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>945</v>
+        <v>692</v>
       </c>
       <c r="C4" t="n">
-        <v>1647</v>
+        <v>1728</v>
       </c>
       <c r="D4" t="n">
-        <v>1912</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4730</v>
+        <v>3056</v>
       </c>
       <c r="C2" t="n">
-        <v>4723</v>
+        <v>3166</v>
       </c>
       <c r="D2" t="n">
-        <v>21392</v>
+        <v>30355</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3435</v>
+        <v>2918</v>
       </c>
       <c r="C3" t="n">
-        <v>3455</v>
+        <v>4125</v>
       </c>
       <c r="D3" t="n">
-        <v>9163</v>
+        <v>6888</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2016</v>
+        <v>1852</v>
       </c>
       <c r="C4" t="n">
-        <v>3052</v>
+        <v>3628</v>
       </c>
       <c r="D4" t="n">
-        <v>2656</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>440</v>
+        <v>341</v>
       </c>
       <c r="C5" t="n">
-        <v>996</v>
+        <v>1078</v>
       </c>
       <c r="D5" t="n">
-        <v>1280</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4565</v>
+        <v>1732</v>
       </c>
       <c r="C2" t="n">
-        <v>10984</v>
+        <v>7485</v>
       </c>
       <c r="D2" t="n">
-        <v>25747</v>
+        <v>28514</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3329</v>
+        <v>2465</v>
       </c>
       <c r="C3" t="n">
-        <v>3575</v>
+        <v>3103</v>
       </c>
       <c r="D3" t="n">
-        <v>10376</v>
+        <v>10146</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2320</v>
+        <v>2063</v>
       </c>
       <c r="C4" t="n">
-        <v>3205</v>
+        <v>3838</v>
       </c>
       <c r="D4" t="n">
-        <v>3762</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>927</v>
       </c>
       <c r="C5" t="n">
-        <v>2031</v>
+        <v>2475</v>
       </c>
       <c r="D5" t="n">
-        <v>1466</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="C6" t="n">
-        <v>653</v>
+        <v>697</v>
       </c>
       <c r="D6" t="n">
-        <v>959</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5732</v>
+        <v>3063</v>
       </c>
       <c r="C2" t="n">
-        <v>16249</v>
+        <v>6130</v>
       </c>
       <c r="D2" t="n">
-        <v>33489</v>
+        <v>22577</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2861</v>
+        <v>1764</v>
       </c>
       <c r="C3" t="n">
-        <v>6030</v>
+        <v>4723</v>
       </c>
       <c r="D3" t="n">
-        <v>11273</v>
+        <v>12223</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1742</v>
+        <v>1953</v>
       </c>
       <c r="C4" t="n">
-        <v>2768</v>
+        <v>3326</v>
       </c>
       <c r="D4" t="n">
-        <v>4234</v>
+        <v>4264</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>868</v>
+        <v>1270</v>
       </c>
       <c r="C5" t="n">
-        <v>1937</v>
+        <v>3143</v>
       </c>
       <c r="D5" t="n">
-        <v>1461</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>294</v>
+        <v>484</v>
       </c>
       <c r="C6" t="n">
-        <v>907</v>
+        <v>1593</v>
       </c>
       <c r="D6" t="n">
-        <v>795</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>317</v>
+        <v>495</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4793</v>
+        <v>3946</v>
       </c>
       <c r="C2" t="n">
-        <v>11362</v>
+        <v>9963</v>
       </c>
       <c r="D2" t="n">
-        <v>40591</v>
+        <v>28229</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3576</v>
+        <v>1944</v>
       </c>
       <c r="C3" t="n">
-        <v>10331</v>
+        <v>4730</v>
       </c>
       <c r="D3" t="n">
-        <v>14175</v>
+        <v>12873</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2019</v>
+        <v>1609</v>
       </c>
       <c r="C4" t="n">
-        <v>4683</v>
+        <v>3935</v>
       </c>
       <c r="D4" t="n">
-        <v>5483</v>
+        <v>5468</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1165</v>
+        <v>1407</v>
       </c>
       <c r="C5" t="n">
-        <v>2383</v>
+        <v>3168</v>
       </c>
       <c r="D5" t="n">
-        <v>1975</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>534</v>
+        <v>749</v>
       </c>
       <c r="C6" t="n">
-        <v>1470</v>
+        <v>2320</v>
       </c>
       <c r="D6" t="n">
-        <v>911</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>256</v>
       </c>
       <c r="C7" t="n">
-        <v>652</v>
+        <v>1011</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>385</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4818</v>
+        <v>3454</v>
       </c>
       <c r="C2" t="n">
-        <v>9404</v>
+        <v>6137</v>
       </c>
       <c r="D2" t="n">
-        <v>33415</v>
+        <v>22152</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3432</v>
+        <v>2729</v>
       </c>
       <c r="C3" t="n">
-        <v>9437</v>
+        <v>7658</v>
       </c>
       <c r="D3" t="n">
-        <v>17380</v>
+        <v>14310</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2404</v>
+        <v>1300</v>
       </c>
       <c r="C4" t="n">
-        <v>7685</v>
+        <v>5534</v>
       </c>
       <c r="D4" t="n">
-        <v>6985</v>
+        <v>5050</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1389</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>3591</v>
+        <v>2273</v>
       </c>
       <c r="D5" t="n">
-        <v>2535</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>771</v>
+        <v>236</v>
       </c>
       <c r="C6" t="n">
-        <v>1935</v>
+        <v>990</v>
       </c>
       <c r="D6" t="n">
-        <v>1092</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>1076</v>
+        <v>377</v>
       </c>
       <c r="D7" t="n">
-        <v>612</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>460</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
